--- a/excel/pacifico-dex-sociedad-anonima-cerrada_capacitaciones.xlsx
+++ b/excel/pacifico-dex-sociedad-anonima-cerrada_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001675881</t>
+          <t>C001721401</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001675881 - MALDONADO DE VASQUEZ FANI ANITA</t>
+          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001682236</t>
+          <t>C001736862</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001682236 - JURADO ACUNA NURIA MAGJURI</t>
+          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001707468</t>
+          <t>C001749956</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
+          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001721401</t>
+          <t>C004021977</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
+          <t>C004021977 - REVATTA ROMANI PATTY LISETH</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001736862</t>
+          <t>C004030181</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
+          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C004030181</t>
+          <t>C004054129</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
+          <t>C004054129 - HUANCAHUARI BENDEZU LUIS FELIPE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001749956</t>
+          <t>C004165676</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
+          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C004165676</t>
+          <t>C004201099</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
+          <t>C004201099 - GUTIERREZ CABALLA INDRID VIVIANA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004201099</t>
+          <t>C001443020</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004201099 - GUTIERREZ CABALLA INDRID VIVIANA</t>
+          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1460,13 +1460,17 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1502,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C004021977</t>
+          <t>C001448001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C004021977 - REVATTA ROMANI PATTY LISETH</t>
+          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1588,12 +1592,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C004054129</t>
+          <t>C001650094</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C004054129 - HUANCAHUARI BENDEZU LUIS FELIPE</t>
+          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1678,12 +1682,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001650094</t>
+          <t>C001675881</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
+          <t>C001675881 - MALDONADO DE VASQUEZ FANI ANITA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1768,12 +1772,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001443020</t>
+          <t>C001682236</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
+          <t>C001682236 - JURADO ACUNA NURIA MAGJURI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1820,17 +1824,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001448001</t>
+          <t>C001707468</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
+          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C000872571</t>
+          <t>C004172308</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C000872571 - RAMIREZ PARIONA CIRILO</t>
+          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C001360989</t>
+          <t>C001754687</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
+          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C001342177</t>
+          <t>C001749432</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C001342177 - HERNANDEZ GAMBOA MARTHA MIRIAM</t>
+          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C001376387</t>
+          <t>C004030175</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
+          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001494780</t>
+          <t>C004044927</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
+          <t>C004044927 - LLANA DE ARONI YNES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001489093</t>
+          <t>C001494780</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
+          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C004030175</t>
+          <t>C001489093</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
+          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C004044927</t>
+          <t>C001678425</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C004044927 - LLANA DE ARONI YNES</t>
+          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001754687</t>
+          <t>C001216310</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
+          <t>C001216310 - VENTURA SOTO JULIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001749432</t>
+          <t>C001360989</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
+          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001678425</t>
+          <t>C001342177</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
+          <t>C001342177 - HERNANDEZ GAMBOA MARTHA MIRIAM</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C004172308</t>
+          <t>C001376387</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
+          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001216310</t>
+          <t>C000872558</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001216310 - VENTURA SOTO JULIA</t>
+          <t>C000872558 - ROJAS CAYLLAHUA DORIS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C000874090</t>
+          <t>C000872571</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
+          <t>C000872571 - RAMIREZ PARIONA CIRILO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C000878043</t>
+          <t>C000874090</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C000878043 - VILCA TINEO JUAN</t>
+          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C000878065</t>
+          <t>C000878043</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C000878065 - VILCA TINEO NIEVES</t>
+          <t>C000878043 - VILCA TINEO JUAN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C000882008</t>
+          <t>C000878065</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C000882008 - DE LA CRUZ DE HUAMAN CERAFINA</t>
+          <t>C000878065 - VILCA TINEO NIEVES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C000872558</t>
+          <t>C000882008</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C000872558 - ROJAS CAYLLAHUA DORIS</t>
+          <t>C000882008 - DE LA CRUZ DE HUAMAN CERAFINA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001393042</t>
+          <t>C001017106</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
+          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C004242029</t>
+          <t>C000876293</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
+          <t>C000876293 - MORAN CRUCES GLORIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C000881763</t>
+          <t>C000880873</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
+          <t>C000880873 - ALTAMIRANO TINEO JORGE LUIS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C004236587</t>
+          <t>C000881763</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C004236587 - ANDRES MENESES CECILIA YGNACIA</t>
+          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4605,11 +4605,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -4668,12 +4664,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C000876293</t>
+          <t>C001442207</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C000876293 - MORAN CRUCES GLORIA</t>
+          <t>C001442207 - HERRERA CABRERA JAIME ANTONIO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4758,12 +4754,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C000880873</t>
+          <t>C001393042</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C000880873 - ALTAMIRANO TINEO JORGE LUIS</t>
+          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4848,12 +4844,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001017106</t>
+          <t>C001491104</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
+          <t>C001491104 - ANGULO ESPINO MANUEL JESUS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5028,12 +5024,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001491104</t>
+          <t>C004197824</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C001491104 - ANGULO ESPINO MANUEL JESUS</t>
+          <t>C004197824 - CHOQUE OLAECHEA MARIA TERESA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5118,12 +5114,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001442207</t>
+          <t>C004236587</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001442207 - HERRERA CABRERA JAIME ANTONIO</t>
+          <t>C004236587 - ANDRES MENESES CECILIA YGNACIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5149,7 +5145,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C004197824</t>
+          <t>C004242029</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C004197824 - CHOQUE OLAECHEA MARIA TERESA</t>
+          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001740525</t>
+          <t>C004183715</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
+          <t>C004183715 - DE LA TORRE SOTO ALAIN DIEGO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -5388,12 +5388,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001561985</t>
+          <t>C004030176</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
+          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001612526</t>
+          <t>C001561985</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
+          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004183039</t>
+          <t>C001016032</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004183039 - GARCIA MOQUILLAZA JANETH VANESSA</t>
+          <t>C001016032 - CARBAJAL HUACHIN FREDDY PROSPERO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004030168</t>
+          <t>C001740525</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
+          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001752823</t>
+          <t>C001612526</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001752823 - TORRES ARONI HUGO PERCY</t>
+          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C000881973</t>
+          <t>C004183039</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C000881973 - GARCIA AURIS JUAN</t>
+          <t>C004183039 - GARCIA MOQUILLAZA JANETH VANESSA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001492921</t>
+          <t>C004030168</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
+          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001469510</t>
+          <t>C004030170</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
+          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C004030176</t>
+          <t>C001752823</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
+          <t>C001752823 - TORRES ARONI HUGO PERCY</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C004030170</t>
+          <t>C001492921</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
+          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C004183715</t>
+          <t>C001469510</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C004183715 - DE LA TORRE SOTO ALAIN DIEGO</t>
+          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001016032</t>
+          <t>C000875504</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C001016032 - CARBAJAL HUACHIN FREDDY PROSPERO</t>
+          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C000875504</t>
+          <t>C000881973</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
+          <t>C000881973 - GARCIA AURIS JUAN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C004036835</t>
+          <t>C001215558</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C004036835 - QUISPE FLORES LUIS OCTAVIO</t>
+          <t>C001215558 -  JIMENEZ ACASIETE MARIELA YANET</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10030,13 +10030,17 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10068,12 +10072,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C004060670</t>
+          <t>C001516381</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
+          <t>C001516381 - YARMA ECHACCAYA GISSELA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10114,23 +10118,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10162,12 +10162,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001516381</t>
+          <t>C000872290</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001516381 - YARMA ECHACCAYA GISSELA</t>
+          <t>C000872290 - INCA RAMOS DE QUILLAS VILMA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S108" t="inlineStr"/>
@@ -10252,12 +10252,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001215558</t>
+          <t>C000872287</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C001215558 -  JIMENEZ ACASIETE MARIELA YANET</t>
+          <t>C000872287 - LARA SALAZAR ISABEL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10304,17 +10304,13 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10346,12 +10342,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C000872290</t>
+          <t>C000882032</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C000872290 - INCA RAMOS DE QUILLAS VILMA</t>
+          <t>C000882032 -  GUTIERREZ ROJAS TEODORO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10436,12 +10432,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C000872287</t>
+          <t>C001398453</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C000872287 - LARA SALAZAR ISABEL</t>
+          <t>C001398453 - ASTOCAZA LUJAN MARIA ELENA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10526,12 +10522,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C000882032</t>
+          <t>C001218188</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C000882032 -  GUTIERREZ ROJAS TEODORO</t>
+          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10616,12 +10612,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C001398453</t>
+          <t>C001330256</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C001398453 - ASTOCAZA LUJAN MARIA ELENA</t>
+          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10668,13 +10664,17 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10706,12 +10706,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C001218188</t>
+          <t>C001489520</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
+          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10758,13 +10758,17 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10796,12 +10800,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C001330256</t>
+          <t>C001453033</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
+          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10848,17 +10852,13 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10890,12 +10890,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001549391</t>
+          <t>C001708107</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
+          <t>C001708107 - COELLO TINEO TONY WILLIANS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001489520</t>
+          <t>C001708342</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
+          <t>C001708342 - MONTAÑO FLORES NELLY MELIANA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11032,17 +11032,13 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11074,12 +11070,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001453033</t>
+          <t>C001549391</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
+          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11434,12 +11430,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C004041142</t>
+          <t>C004036835</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>C004041142 - HUAMAN BERROCAL GLORIA ROSARIO</t>
+          <t>C004036835 - QUISPE FLORES LUIS OCTAVIO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -11524,12 +11520,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C004014409</t>
+          <t>C004060670</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C004014409 - HUASHUAYLLO RAMOS SONIA</t>
+          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11555,11 +11551,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -11580,13 +11572,17 @@
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11618,12 +11614,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001752251</t>
+          <t>C004014409</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
+          <t>C004014409 - HUASHUAYLLO RAMOS SONIA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11649,7 +11645,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -11670,17 +11670,13 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11712,12 +11708,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001708107</t>
+          <t>C004041142</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001708107 - COELLO TINEO TONY WILLIANS</t>
+          <t>C004041142 - HUAMAN BERROCAL GLORIA ROSARIO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11802,12 +11798,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001708342</t>
+          <t>C001752251</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001708342 - MONTAÑO FLORES NELLY MELIANA</t>
+          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11854,13 +11850,17 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C004176366</t>
+          <t>C004161347</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
+          <t>C004161347 - CCORA SOTO AYDEE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004161347</t>
+          <t>C004176366</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C004161347 - CCORA SOTO AYDEE</t>
+          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C004240818</t>
+          <t>C000875697</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
+          <t>C000875697 - PIZARRO MANTARI MARIA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -13982,12 +13982,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C001098861</t>
+          <t>C000881361</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C001098861 - DE LA CRUZ DE JANAMPA VICTORIA ANTONIA</t>
+          <t>C000881361 - CONISLLA FLORES BLANCA MARLENY</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14034,13 +14034,17 @@
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14072,12 +14076,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C000875697</t>
+          <t>C000881938</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C000875697 - PIZARRO MANTARI MARIA</t>
+          <t>C000881938 - MONTOYA CARRIZALES ROSA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14118,7 +14122,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S151" t="inlineStr"/>
@@ -14166,12 +14170,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C000881361</t>
+          <t>C001098861</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C000881361 - CONISLLA FLORES BLANCA MARLENY</t>
+          <t>C001098861 - DE LA CRUZ DE JANAMPA VICTORIA ANTONIA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14218,17 +14222,13 @@
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14260,12 +14260,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C000881938</t>
+          <t>C001218181</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C000881938 - MONTOYA CARRIZALES ROSA</t>
+          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14306,23 +14306,19 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14354,12 +14350,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001385265</t>
+          <t>C001445551</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
+          <t>C001445551 - HUAMAN HERNANDEZ MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14444,12 +14440,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C001218181</t>
+          <t>C001385265</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
+          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14534,12 +14530,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C001445551</t>
+          <t>C001469894</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>C001445551 - HUAMAN HERNANDEZ MARCOS ANTONIO</t>
+          <t>C001469894 - PACHECO LAGOS BERTHA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14624,12 +14620,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C001469894</t>
+          <t>C001472446</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C001469894 - PACHECO LAGOS BERTHA</t>
+          <t>C001472446 - HUAROTO HERNANDEZ CEFERINO FELIPE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -14714,12 +14710,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001472446</t>
+          <t>C001532427</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>C001472446 - HUAROTO HERNANDEZ CEFERINO FELIPE</t>
+          <t>C001532427 - GAVILAN BENDEZU MAYRA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -14804,12 +14800,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001532427</t>
+          <t>C001622444</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>C001532427 - GAVILAN BENDEZU MAYRA</t>
+          <t>C001622444 - SUMARI QUISPE JURICA JANETT</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -14894,12 +14890,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C001649207</t>
+          <t>C001618635</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
+          <t>C001618635 - NEYRA NEYRA TOMASA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14984,12 +14980,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C001622444</t>
+          <t>C001649207</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C001622444 - SUMARI QUISPE JURICA JANETT</t>
+          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15074,12 +15070,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>C001618635</t>
+          <t>C001559864</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>C001618635 - NEYRA NEYRA TOMASA</t>
+          <t>C001559864 - MATIAS ROJAS LUIS ANGEL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -15164,12 +15160,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001559864</t>
+          <t>C004196755</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C001559864 - MATIAS ROJAS LUIS ANGEL</t>
+          <t>C004196755 - HUAYHUA ROMERO EDITH</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15254,12 +15250,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C004182387</t>
+          <t>C004200425</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>C004182387 - PEREZ CHOQUE NANCY ANGELICA</t>
+          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15344,12 +15340,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C004196755</t>
+          <t>C004191869</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>C004196755 - HUAYHUA ROMERO EDITH</t>
+          <t>C004191869 - QUICANO QUISPE BETTY CECILIA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15434,12 +15430,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C004193232</t>
+          <t>C004191872</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C004193232 - MASCCO HUAULLA MILAGROS YURIKO</t>
+          <t>C004191872 - CONDE HUAMANI ESMERALDA OCHYN</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15524,12 +15520,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C004191869</t>
+          <t>C004193232</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C004191869 - QUICANO QUISPE BETTY CECILIA</t>
+          <t>C004193232 - MASCCO HUAULLA MILAGROS YURIKO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -15614,12 +15610,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C004191872</t>
+          <t>C004240818</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C004191872 - CONDE HUAMANI ESMERALDA OCHYN</t>
+          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -15666,13 +15662,17 @@
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15704,12 +15704,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C004200425</t>
+          <t>C004182387</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
+          <t>C004182387 - PEREZ CHOQUE NANCY ANGELICA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>C001360879</t>
+          <t>C001540447</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
+          <t>C001540447 - INVERSIONES ROCELI S.A.C.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -16762,17 +16762,13 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16804,12 +16800,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C001197394</t>
+          <t>C001572913</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
+          <t>C001572913 - CCAYCO CANALES MARISA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -16856,13 +16852,17 @@
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16894,12 +16894,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C001540447</t>
+          <t>C001577373</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C001540447 - INVERSIONES ROCELI S.A.C.</t>
+          <t>C001577373 - CONTRERAS GUERRERO LISBET</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -16925,7 +16925,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -16946,13 +16950,17 @@
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16984,12 +16992,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001535865</t>
+          <t>C001612448</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001535865 - NANAJUARI CALDERON HILDA YOVANA</t>
+          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17036,13 +17044,17 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17074,12 +17086,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001612448</t>
+          <t>C001492706</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
+          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17168,12 +17180,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001572913</t>
+          <t>C001535865</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001572913 - CCAYCO CANALES MARISA</t>
+          <t>C001535865 - NANAJUARI CALDERON HILDA YOVANA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17220,17 +17232,13 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17262,12 +17270,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C001577373</t>
+          <t>C001481930</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C001577373 - CONTRERAS GUERRERO LISBET</t>
+          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -17293,11 +17301,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -17323,12 +17327,12 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17360,12 +17364,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C001481930</t>
+          <t>C001360879</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
+          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -17454,12 +17458,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C001492706</t>
+          <t>C001197394</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
+          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -17506,17 +17510,13 @@
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -18006,12 +18006,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C004206356</t>
+          <t>C004218242</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C004206356 - MINAS CHACALIAZA SILVIA MARIELA</t>
+          <t>C004218242 - JHONG RAFFO CRISTIABEL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18058,13 +18058,17 @@
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18096,12 +18100,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>C004218242</t>
+          <t>C004209286</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C004218242 - JHONG RAFFO CRISTIABEL</t>
+          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -18190,12 +18194,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C004209286</t>
+          <t>C004206356</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
+          <t>C004206356 - MINAS CHACALIAZA SILVIA MARIELA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -18242,17 +18246,13 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -19200,12 +19200,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001761926</t>
+          <t>C004023355</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
+          <t>C004023355 - DELGADO CALLE ENA LUZ</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -19294,12 +19294,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C004023355</t>
+          <t>C001761926</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C004023355 - DELGADO CALLE ENA LUZ</t>
+          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -21138,12 +21138,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001489958</t>
+          <t>C001445071</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C001489958 - HINOSTROZA VILCAPUMA LUZMILA ALEXANDRA</t>
+          <t>C001445071 - MEJIA GALINDO FACUNDINA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21190,13 +21190,17 @@
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21228,12 +21232,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001492696</t>
+          <t>C001397200</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
+          <t>C001397200 - PUJAIS VASQUEZ ROSANA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -21318,12 +21322,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C001551423</t>
+          <t>C001489958</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001551423 - MATA CUPE DYLAN RENATO</t>
+          <t>C001489958 - HINOSTROZA VILCAPUMA LUZMILA ALEXANDRA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21408,12 +21412,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C001539717</t>
+          <t>C001492696</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
+          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -21460,17 +21464,13 @@
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21502,12 +21502,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001563527</t>
+          <t>C001551423</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001563527 - MINAYA RIOS DE MOGOLLON JESSICA VANESA</t>
+          <t>C001551423 - MATA CUPE DYLAN RENATO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -21554,17 +21554,13 @@
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21596,12 +21592,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001445071</t>
+          <t>C001563527</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001445071 - MEJIA GALINDO FACUNDINA</t>
+          <t>C001563527 - MINAYA RIOS DE MOGOLLON JESSICA VANESA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -21690,12 +21686,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001397200</t>
+          <t>C001539717</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001397200 - PUJAIS VASQUEZ ROSANA</t>
+          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -21742,13 +21738,17 @@
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22058,12 +22058,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C004171458</t>
+          <t>C004203037</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
+          <t>C004203037 - DIAZ CHUQUIHUACCHA FLOR LILIANA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S238" t="inlineStr"/>
@@ -22152,12 +22152,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C004203037</t>
+          <t>C001708339</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C004203037 - DIAZ CHUQUIHUACCHA FLOR LILIANA</t>
+          <t>C001708339 - ESCALANTE SALCEDO MILTON EUSTAQUIO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -22204,17 +22204,13 @@
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22246,12 +22242,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001708339</t>
+          <t>C001709581</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001708339 - ESCALANTE SALCEDO MILTON EUSTAQUIO</t>
+          <t>C001709581 - QUINONEZ ANTAYA EVA MARGARITA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -22298,13 +22294,17 @@
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U240" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22336,12 +22336,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C001749448</t>
+          <t>C001539721</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
+          <t>C001539721 - ALLCCAHUAMAN CAHUANA KAREN LISSET</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22388,17 +22388,13 @@
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22520,12 +22516,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>C001539721</t>
+          <t>C001749448</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C001539721 - ALLCCAHUAMAN CAHUANA KAREN LISSET</t>
+          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -22572,13 +22568,17 @@
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22610,12 +22610,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C004044936</t>
+          <t>C001752398</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
+          <t>C001752398 - HUALPA GUEVARA ANDERSON PAUL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -22667,12 +22667,12 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C004059422</t>
+          <t>C004009751</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
+          <t>C004009751 - CULE QUISPE JOSE</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -22761,12 +22761,12 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22798,12 +22798,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001709581</t>
+          <t>C004044936</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C001709581 - QUINONEZ ANTAYA EVA MARGARITA</t>
+          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -22855,12 +22855,12 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22892,12 +22892,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001752398</t>
+          <t>C004059422</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C001752398 - HUALPA GUEVARA ANDERSON PAUL</t>
+          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -22949,12 +22949,12 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22986,12 +22986,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C004009751</t>
+          <t>C004171458</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C004009751 - CULE QUISPE JOSE</t>
+          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23032,7 +23032,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S248" t="inlineStr"/>
@@ -23043,12 +23043,12 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24192,12 +24192,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C000875203</t>
+          <t>C000882553</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C000875203 - ROSAS NIETO JUAN</t>
+          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -24244,13 +24244,17 @@
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24282,12 +24286,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C000877090</t>
+          <t>C000883040</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
+          <t>C000883040 - YALLE CASAVILCA NELIO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24376,12 +24380,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C000882553</t>
+          <t>C000877090</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
+          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -24470,12 +24474,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C000883040</t>
+          <t>C000875203</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C000883040 - YALLE CASAVILCA NELIO</t>
+          <t>C000875203 - ROSAS NIETO JUAN</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -24522,17 +24526,13 @@
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr"/>
       <c r="V264" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25316,12 +25316,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C004243810</t>
+          <t>C004207402</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
+          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25368,17 +25368,13 @@
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr"/>
       <c r="V273" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25410,12 +25406,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C004239540</t>
+          <t>C004216987</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
+          <t>C004216987 - BENAVIDES SOTO LIDIA ROCIO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -25467,12 +25463,12 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25504,12 +25500,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C004216987</t>
+          <t>C004243810</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C004216987 - BENAVIDES SOTO LIDIA ROCIO</t>
+          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -25561,12 +25557,12 @@
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25598,12 +25594,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C004207402</t>
+          <t>C004239540</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
+          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -25650,13 +25646,17 @@
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25688,12 +25688,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C004191301</t>
+          <t>C000881830</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
+          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -25740,13 +25740,17 @@
       <c r="S277" t="inlineStr"/>
       <c r="T277" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25778,12 +25782,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>C004191304</t>
+          <t>C000874788</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
+          <t>C000874788 - HUAMANI AVALOS NURY JULY</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -25835,12 +25839,12 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25872,12 +25876,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C000874788</t>
+          <t>C000874272</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C000874788 - HUAMANI AVALOS NURY JULY</t>
+          <t>C000874272 - LEGUA MEJIA FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -25903,7 +25907,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
@@ -25924,17 +25932,13 @@
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr"/>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25966,12 +25970,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C000874272</t>
+          <t>C004191301</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C000874272 - LEGUA MEJIA FLOR DE MARIA</t>
+          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -25997,11 +26001,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
@@ -26060,12 +26060,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C004179837</t>
+          <t>C004191304</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C004179837 - CONCA FLORES DORA ESTHER</t>
+          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -26117,12 +26117,12 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26154,12 +26154,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C000881830</t>
+          <t>C004179837</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
+          <t>C004179837 - CONCA FLORES DORA ESTHER</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -26211,12 +26211,12 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26248,12 +26248,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001708610</t>
+          <t>C001709978</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001708610 - SALAZAR YALLE FIORELLA ESTEFANI</t>
+          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -26300,13 +26300,17 @@
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26338,12 +26342,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C001709978</t>
+          <t>C001708610</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
+          <t>C001708610 - SALAZAR YALLE FIORELLA ESTEFANI</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -26390,17 +26394,13 @@
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26432,12 +26432,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C001683408</t>
+          <t>C001615633</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
+          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S285" t="inlineStr"/>
@@ -26526,12 +26526,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C004192500</t>
+          <t>C001683408</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>C004192500 - CORTEZ FLORES PATRICIA ELIZABETH</t>
+          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -26583,12 +26583,12 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26620,12 +26620,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001471930</t>
+          <t>C004192500</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C001471930 - VICUNA REYES RAMON LINO</t>
+          <t>C004192500 - CORTEZ FLORES PATRICIA ELIZABETH</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -26672,13 +26672,17 @@
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26710,12 +26714,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C001722065</t>
+          <t>C001471930</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
+          <t>C001471930 - VICUNA REYES RAMON LINO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -26741,11 +26745,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
@@ -26766,17 +26766,13 @@
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26808,12 +26804,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C001506102</t>
+          <t>C001722065</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>C001506102 - QUICHUA ARROYO MARILU</t>
+          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -26839,7 +26835,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
@@ -26902,12 +26902,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C001284711</t>
+          <t>C001506102</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
+          <t>C001506102 - QUICHUA ARROYO MARILU</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -26996,12 +26996,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C001547860</t>
+          <t>C001284711</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
+          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -27090,12 +27090,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001615633</t>
+          <t>C001547860</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
+          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S292" t="inlineStr"/>
@@ -27184,12 +27184,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C000882632</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>C000882632 - RAMIREZ VICU A JULIA</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -27368,12 +27368,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C000874379</t>
+          <t>C000882632</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
+          <t>C000882632 - RAMIREZ VICU A JULIA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -27420,13 +27420,17 @@
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27458,12 +27462,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C000874379</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -27510,17 +27514,13 @@
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr"/>
       <c r="V296" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001390551</t>
+          <t>C001374929</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
+          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -27698,17 +27698,13 @@
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27740,12 +27736,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001374929</t>
+          <t>C001390551</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
+          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -27792,13 +27788,17 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28844,12 +28844,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C000882129</t>
+          <t>C000882854</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C000882129 - EL GOLFO SAC</t>
+          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C000881032</t>
+          <t>C000882129</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
+          <t>C000882129 - EL GOLFO SAC</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -29024,12 +29024,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>C000882854</t>
+          <t>C000881032</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
+          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">

--- a/excel/pacifico-dex-sociedad-anonima-cerrada_capacitaciones.xlsx
+++ b/excel/pacifico-dex-sociedad-anonima-cerrada_capacitaciones.xlsx
@@ -1060,12 +1060,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001552894</t>
+          <t>C001638974</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
+          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1112,13 +1112,17 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001638974</t>
+          <t>C001552894</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
+          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1202,17 +1206,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001715921</t>
+          <t>C001748916</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001715921 - APARCANA PISCONTE LUIS ANTONIO</t>
+          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C004012811</t>
+          <t>C001737288</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C004012811 - LAZARO FERNANDEZ NEZARETH JOSUE</t>
+          <t>C001737288 - ANTEZANA MENDOZA SILVIA NANCY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1369,7 +1369,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1432,12 +1436,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004016410</t>
+          <t>C001736860</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004016410 - MUCHAYPIÑA MEDINA BERTHA HERLINDA</t>
+          <t>C001736860 - PUPPI DE GALLEGOS RODELINDA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1484,17 +1488,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001748916</t>
+          <t>C001733616</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
+          <t>C001733616 - RUEDA GARCIA CECILIA JESSICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1578,17 +1578,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1616,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001736860</t>
+          <t>C001715921</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001736860 - PUPPI DE GALLEGOS RODELINDA ALEJANDRINA</t>
+          <t>C001715921 - APARCANA PISCONTE LUIS ANTONIO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1672,13 +1668,17 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001737288</t>
+          <t>C004203039</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001737288 - ANTEZANA MENDOZA SILVIA NANCY</t>
+          <t>C004203039 - QUINTANILLA YALLE CARMEN NANCY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1741,11 +1741,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1766,17 +1762,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1800,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001733616</t>
+          <t>C004016410</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001733616 - RUEDA GARCIA CECILIA JESSICA</t>
+          <t>C004016410 - MUCHAYPIÑA MEDINA BERTHA HERLINDA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1860,13 +1852,17 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1894,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004223837</t>
+          <t>C004012811</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004223837 - MAVILA ALVAREZ WALTER WILFREDO</t>
+          <t>C004012811 - LAZARO FERNANDEZ NEZARETH JOSUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,13 +1946,17 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004216610</t>
+          <t>C004223837</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C004216610 - PEÑA HERNANDEZ MARIA CONSUELO</t>
+          <t>C004223837 - MAVILA ALVAREZ WALTER WILFREDO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2040,17 +2040,13 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2078,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004207401</t>
+          <t>C004216610</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004207401 - CORTEZ COCHEVARE ALEXANDRA NATALIA</t>
+          <t>C004216610 - PEÑA HERNANDEZ MARIA CONSUELO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2134,13 +2130,17 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004203039</t>
+          <t>C004207401</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C004203039 - QUINTANILLA YALLE CARMEN NANCY</t>
+          <t>C004207401 - CORTEZ COCHEVARE ALEXANDRA NATALIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001174355</t>
+          <t>C001399017</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001174355 - HUAMAN PALLIN JHON YSACC</t>
+          <t>C001399017 - LLOCCLLA HUARANCCA JOSE LUIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2314,17 +2314,13 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2356,12 +2352,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001399017</t>
+          <t>C001174355</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001399017 - LLOCCLLA HUARANCCA JOSE LUIS</t>
+          <t>C001174355 - HUAMAN PALLIN JHON YSACC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2408,13 +2404,17 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001374929</t>
+          <t>C004203048</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
+          <t>C004203048 - HUAMANI RAMOS ROSULA CRISTINA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004203048</t>
+          <t>C004243810</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C004203048 - HUAMANI RAMOS ROSULA CRISTINA</t>
+          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004243810</t>
+          <t>C004173905</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
+          <t>C004173905 - BENDEZU PARIONA LEONOR ISABEL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001580075</t>
+          <t>C001672172</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001580075 - PAYTAN CABALLA GULIANA SALLY</t>
+          <t>C001672172 - TENORIO SORIA LILY AMPARO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001641580</t>
+          <t>C001657060</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001641580 - QUISPE PILCO FELIX ALBERTO</t>
+          <t>C001657060 - URIBE MITACC MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001672172</t>
+          <t>C001733058</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001672172 - TENORIO SORIA LILY AMPARO</t>
+          <t>C001733058 - HUAMAN ANDRES MERCEDES DALILA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001657060</t>
+          <t>C004032075</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001657060 - URIBE MITACC MARIA MAGDALENA</t>
+          <t>C004032075 - DISTRIBUIDORA COMERCIAL ALBITES S.A.C.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001398064</t>
+          <t>C001754826</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001398064 - PEREZ GUTIERREZ EDGAR ELIAS</t>
+          <t>C001754826 - NIETO HUAMANI GERALDINE LISETTE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001494647</t>
+          <t>C004014091</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001494647 - QUISPE CARHUAYO MARIANA MAITE</t>
+          <t>C004014091 - DISTRIBUIDORA JOSUE &amp; DAVID E.I.R.L.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3512,13 +3512,17 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3554,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C004044917</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C004044917 - NEYRA AYBAR JANET MARTHA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3607,12 +3611,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3648,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C000874079</t>
+          <t>C001580075</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C000874079 - ARMACANQUI VENTURA EDGAR</t>
+          <t>C001580075 - PAYTAN CABALLA GULIANA SALLY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3696,17 +3700,13 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C000880953</t>
+          <t>C001641580</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C000880953 - VILCA DE AMARCANQUI ANTONIA</t>
+          <t>C001641580 - QUISPE PILCO FELIX ALBERTO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3774,17 +3774,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C004173905</t>
+          <t>C001494647</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C004173905 - BENDEZU PARIONA LEONOR ISABEL</t>
+          <t>C001494647 - QUISPE CARHUAYO MARIANA MAITE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3880,17 +3880,13 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3918,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004032075</t>
+          <t>C001374929</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C004032075 - DISTRIBUIDORA COMERCIAL ALBITES S.A.C.</t>
+          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3974,13 +3970,17 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001754826</t>
+          <t>C001398064</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001754826 - NIETO HUAMANI GERALDINE LISETTE</t>
+          <t>C001398064 - PEREZ GUTIERREZ EDGAR ELIAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004014091</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C004014091 - DISTRIBUIDORA JOSUE &amp; DAVID E.I.R.L.</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4200,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004044917</t>
+          <t>C000874079</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004044917 - NEYRA AYBAR JANET MARTHA</t>
+          <t>C000874079 - ARMACANQUI VENTURA EDGAR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001733058</t>
+          <t>C000880953</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001733058 - HUAMAN ANDRES MERCEDES DALILA</t>
+          <t>C000880953 - VILCA DE AMARCANQUI ANTONIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4330,17 +4330,17 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001721401</t>
+          <t>C001707468</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
+          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4436,17 +4436,13 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4474,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001736862</t>
+          <t>C001721401</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
+          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4530,13 +4526,17 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4568,12 +4568,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001749956</t>
+          <t>C001736862</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
+          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4620,17 +4620,13 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4658,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C004030181</t>
+          <t>C001749956</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
+          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4719,12 +4715,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4936,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C004165676</t>
+          <t>C004030181</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
+          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5218,12 +5214,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001443020</t>
+          <t>C004165676</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
+          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5275,12 +5271,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5308,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001448001</t>
+          <t>C001443020</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
+          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5406,12 +5402,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001650094</t>
+          <t>C001448001</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
+          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5688,12 +5684,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001707468</t>
+          <t>C001650094</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
+          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5740,13 +5736,17 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C000875215</t>
+          <t>C001274439</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
+          <t>C001274439 - MORAN QUINTANILLA VICTORIA BEBELU</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5830,17 +5830,13 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5872,12 +5868,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C000881032</t>
+          <t>C001372541</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
+          <t>C001372541 - CRUZADO BENDEZU JOSE FROILAN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5962,12 +5958,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C000882553</t>
+          <t>C000875215</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
+          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6056,12 +6052,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C000883040</t>
+          <t>C000881032</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C000883040 - YALLE CASAVILCA NELIO</t>
+          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6108,17 +6104,13 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6142,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001372541</t>
+          <t>C000882553</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001372541 - CRUZADO BENDEZU JOSE FROILAN</t>
+          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6202,13 +6194,17 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6240,12 +6236,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001274439</t>
+          <t>C000883040</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001274439 - MORAN QUINTANILLA VICTORIA BEBELU</t>
+          <t>C000883040 - YALLE CASAVILCA NELIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6292,13 +6288,17 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C000872558</t>
+          <t>C001678425</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C000872558 - ROJAS CAYLLAHUA DORIS</t>
+          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6382,13 +6382,17 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6424,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C000872571</t>
+          <t>C004044927</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C000872571 - RAMIREZ PARIONA CIRILO</t>
+          <t>C004044927 - LLANA DE ARONI YNES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6472,13 +6476,17 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6510,12 +6518,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C000874090</t>
+          <t>C004030175</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
+          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6562,13 +6570,17 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6600,12 +6612,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C000878043</t>
+          <t>C001754687</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C000878043 - VILCA TINEO JUAN</t>
+          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6657,12 +6669,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6694,12 +6706,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C000878065</t>
+          <t>C001749432</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C000878065 - VILCA TINEO NIEVES</t>
+          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6746,13 +6758,17 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6784,12 +6800,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C000882008</t>
+          <t>C004172308</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C000882008 - DE LA CRUZ DE HUAMAN CERAFINA</t>
+          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6878,12 +6894,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001360989</t>
+          <t>C001494780</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
+          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6972,12 +6988,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001376387</t>
+          <t>C001489093</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
+          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7029,12 +7045,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7082,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001216310</t>
+          <t>C001502263</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001216310 - VENTURA SOTO JULIA</t>
+          <t>C001502263 - MATTA ROMERO MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7118,13 +7134,17 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7156,12 +7176,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001342177</t>
+          <t>C001360989</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001342177 - HERNANDEZ GAMBOA MARTHA MIRIAM</t>
+          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7208,13 +7228,17 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7246,12 +7270,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001494780</t>
+          <t>C001342177</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
+          <t>C001342177 - HERNANDEZ GAMBOA MARTHA MIRIAM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7298,17 +7322,13 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7360,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001489093</t>
+          <t>C001376387</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
+          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7397,12 +7417,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7454,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001502263</t>
+          <t>C001216310</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001502263 - MATTA ROMERO MIGUEL ANGEL</t>
+          <t>C001216310 - VENTURA SOTO JULIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7486,17 +7506,13 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7528,12 +7544,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001678425</t>
+          <t>C000872558</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
+          <t>C000872558 - ROJAS CAYLLAHUA DORIS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7580,17 +7596,13 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7622,12 +7634,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001754687</t>
+          <t>C000872571</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
+          <t>C000872571 - RAMIREZ PARIONA CIRILO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7674,17 +7686,13 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7724,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001749432</t>
+          <t>C000874090</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
+          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7768,17 +7776,13 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7814,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C004030175</t>
+          <t>C000878043</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
+          <t>C000878043 - VILCA TINEO JUAN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7867,12 +7871,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7904,12 +7908,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C004044927</t>
+          <t>C000878065</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C004044927 - LLANA DE ARONI YNES</t>
+          <t>C000878065 - VILCA TINEO NIEVES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7956,17 +7960,13 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004172308</t>
+          <t>C000882008</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
+          <t>C000882008 - DE LA CRUZ DE HUAMAN CERAFINA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C001372288</t>
+          <t>C001393042</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C001372288 - QUISPE DE ROMAN MARIA MAGDALENA</t>
+          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8332,17 +8332,13 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8374,12 +8370,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001017106</t>
+          <t>C001372288</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
+          <t>C001372288 - QUISPE DE ROMAN MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8426,13 +8422,17 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C001393042</t>
+          <t>C001017106</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
+          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C004242029</t>
+          <t>C000881763</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
+          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C000881763</t>
+          <t>C004242029</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
+          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001612526</t>
+          <t>C004183715</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
+          <t>C004183715 - DE LA TORRE SOTO ALAIN DIEGO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9264,13 +9264,17 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9302,12 +9306,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001561985</t>
+          <t>C001740525</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
+          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9348,7 +9352,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S96" t="inlineStr"/>
@@ -9396,12 +9400,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001440721</t>
+          <t>C004030176</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001440721 - CAYAMPI BARRIENTOS MARIBEL LUZ</t>
+          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9453,12 +9457,12 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9494,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001016032</t>
+          <t>C001612526</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001016032 - CARBAJAL HUACHIN FREDDY PROSPERO</t>
+          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9580,12 +9584,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001740525</t>
+          <t>C001561985</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
+          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9626,7 +9630,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
@@ -9674,12 +9678,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C004030176</t>
+          <t>C001440721</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
+          <t>C001440721 - CAYAMPI BARRIENTOS MARIBEL LUZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9731,12 +9735,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9768,12 +9772,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C004183715</t>
+          <t>C004183039</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C004183715 - DE LA TORRE SOTO ALAIN DIEGO</t>
+          <t>C004183039 - GARCIA MOQUILLAZA JANETH VANESSA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9825,12 +9829,12 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9866,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C001492921</t>
+          <t>C001752823</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
+          <t>C001752823 - TORRES ARONI HUGO PERCY</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9914,17 +9918,13 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9956,12 +9956,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001469510</t>
+          <t>C004030168</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
+          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10008,17 +10008,13 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10046,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001752823</t>
+          <t>C004030170</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C001752823 - TORRES ARONI HUGO PERCY</t>
+          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10140,12 +10136,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C004030168</t>
+          <t>C001469510</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
+          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10192,13 +10188,17 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10230,12 +10230,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C004030170</t>
+          <t>C001492921</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
+          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10282,13 +10282,17 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10324,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C004183039</t>
+          <t>C000881973</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C004183039 - GARCIA MOQUILLAZA JANETH VANESSA</t>
+          <t>C000881973 - GARCIA AURIS JUAN</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10414,12 +10418,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C000881973</t>
+          <t>C000875504</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C000881973 - GARCIA AURIS JUAN</t>
+          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10471,12 +10475,12 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10508,12 +10512,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C000875504</t>
+          <t>C001016032</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
+          <t>C001016032 - CARBAJAL HUACHIN FREDDY PROSPERO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10560,17 +10564,13 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14604,12 +14604,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C001330256</t>
+          <t>C001218188</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
+          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14698,12 +14698,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001218188</t>
+          <t>C001330256</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
+          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14755,12 +14755,12 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14886,12 +14886,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C001500992</t>
+          <t>C001453033</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>C001500992 - OLIVARES ROMANI GLORIA</t>
+          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14980,12 +14980,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C001453033</t>
+          <t>C001708107</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
+          <t>C001708107 - COELLO TINEO TONY WILLIANS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -15037,12 +15037,12 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15074,12 +15074,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001708107</t>
+          <t>C001708342</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>C001708107 - COELLO TINEO TONY WILLIANS</t>
+          <t>C001708342 - MONTAÑO FLORES NELLY MELIANA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -15126,17 +15126,13 @@
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15168,12 +15164,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001708342</t>
+          <t>C001549391</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>C001708342 - MONTAÑO FLORES NELLY MELIANA</t>
+          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15220,13 +15216,17 @@
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15352,12 +15352,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C001549391</t>
+          <t>C001500992</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
+          <t>C001500992 - OLIVARES ROMANI GLORIA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16104,12 +16104,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C004176366</t>
+          <t>C004161347</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
+          <t>C004161347 - CCORA SOTO AYDEE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16198,12 +16198,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C004161347</t>
+          <t>C004176366</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>C004161347 - CCORA SOTO AYDEE</t>
+          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -16255,12 +16255,12 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16292,12 +16292,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C000872160</t>
+          <t>C004042769</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
+          <t>C004042769 -  JUNES ARROYO LUZ HAYDEE</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -16323,11 +16323,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -16390,12 +16386,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>C001102508</t>
+          <t>C000872160</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>C001102508 - AVALOS PEREZ WILBER LEONARDO</t>
+          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -16421,7 +16417,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C001716613</t>
+          <t>C001102508</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>C001716613 - SAIRITUPAC MOLINA MIRIAN MAGALY</t>
+          <t>C001102508 - AVALOS PEREZ WILBER LEONARDO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -16578,12 +16578,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>C004042769</t>
+          <t>C001716613</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>C004042769 -  JUNES ARROYO LUZ HAYDEE</t>
+          <t>C001716613 - SAIRITUPAC MOLINA MIRIAN MAGALY</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -18070,12 +18070,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C004182387</t>
+          <t>C001752966</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C004182387 - PEREZ CHOQUE NANCY ANGELICA</t>
+          <t>C001752966 - MASCCO HUAULLA JULIA EPIFANIA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -18122,17 +18122,13 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -18164,12 +18160,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C004200425</t>
+          <t>C001714913</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
+          <t>C001714913 - QUISPE TANTA KAREN YESSENIA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -18254,12 +18250,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C004191869</t>
+          <t>C001709603</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C004191869 - QUICANO QUISPE BETTY CECILIA</t>
+          <t>C001709603 - CARDENAS GUTIERREZ LIDIA ALEJANDRA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -18311,12 +18307,12 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18348,12 +18344,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C004191872</t>
+          <t>C001709606</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C004191872 - CONDE HUAMANI ESMERALDA OCHYN</t>
+          <t>C001709606 - FLORES MORON MARIA ESPERANZA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -18394,7 +18390,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S193" t="inlineStr"/>
@@ -18405,12 +18401,12 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18442,12 +18438,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C004196755</t>
+          <t>C001721510</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C004196755 - HUAYHUA ROMERO EDITH</t>
+          <t>C001721510 - PALACIOS LLOCLLA RITA CARMEN</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18488,7 +18484,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
@@ -18499,12 +18495,12 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18536,12 +18532,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>C004193232</t>
+          <t>C004182387</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C004193232 - MASCCO HUAULLA MILAGROS YURIKO</t>
+          <t>C004182387 - PEREZ CHOQUE NANCY ANGELICA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -18630,12 +18626,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C004240818</t>
+          <t>C004200425</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
+          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -18682,17 +18678,13 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -18724,12 +18716,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C001709603</t>
+          <t>C004191869</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C001709603 - CARDENAS GUTIERREZ LIDIA ALEJANDRA</t>
+          <t>C004191869 - QUICANO QUISPE BETTY CECILIA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -18781,12 +18773,12 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18818,12 +18810,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C001709606</t>
+          <t>C004191872</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>C001709606 - FLORES MORON MARIA ESPERANZA</t>
+          <t>C004191872 - CONDE HUAMANI ESMERALDA OCHYN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -18864,7 +18856,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S198" t="inlineStr"/>
@@ -18875,12 +18867,12 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18912,12 +18904,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>C001714913</t>
+          <t>C004196755</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>C001714913 - QUISPE TANTA KAREN YESSENIA</t>
+          <t>C004196755 - HUAYHUA ROMERO EDITH</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -18964,13 +18956,17 @@
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19002,12 +18998,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>C001721510</t>
+          <t>C004193232</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>C001721510 - PALACIOS LLOCLLA RITA CARMEN</t>
+          <t>C004193232 - MASCCO HUAULLA MILAGROS YURIKO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -19048,7 +19044,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S200" t="inlineStr"/>
@@ -19096,12 +19092,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001752966</t>
+          <t>C004240818</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>C001752966 - MASCCO HUAULLA JULIA EPIFANIA</t>
+          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -19148,13 +19144,17 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19460,12 +19460,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>C001218181</t>
+          <t>C001385265</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
+          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -19512,13 +19512,17 @@
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U205" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19550,12 +19554,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C001385265</t>
+          <t>C001532427</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
+          <t>C001532427 - GAVILAN BENDEZU MAYRA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -19607,12 +19611,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19644,12 +19648,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001532427</t>
+          <t>C001559864</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001532427 - GAVILAN BENDEZU MAYRA</t>
+          <t>C001559864 - MATIAS ROJAS LUIS ANGEL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -19701,12 +19705,12 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19738,12 +19742,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001559864</t>
+          <t>C001649207</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C001559864 - MATIAS ROJAS LUIS ANGEL</t>
+          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -19795,12 +19799,12 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19832,12 +19836,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C001649207</t>
+          <t>C001618635</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
+          <t>C001618635 - NEYRA NEYRA TOMASA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -19884,17 +19888,13 @@
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20020,12 +20020,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001618635</t>
+          <t>C001098861</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C001618635 - NEYRA NEYRA TOMASA</t>
+          <t>C001098861 - DE LA CRUZ DE JANAMPA VICTORIA ANTONIA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001098861</t>
+          <t>C001218181</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C001098861 - DE LA CRUZ DE JANAMPA VICTORIA ANTONIA</t>
+          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -20952,12 +20952,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001360879</t>
+          <t>C001572913</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
+          <t>C001572913 - CCAYCO CANALES MARISA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -21046,12 +21046,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001197394</t>
+          <t>C001577373</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
+          <t>C001577373 - CONTRERAS GUERRERO LISBET</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -21077,7 +21077,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
@@ -21103,12 +21107,12 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21140,12 +21144,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001540447</t>
+          <t>C001612448</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C001540447 - INVERSIONES ROCELI S.A.C.</t>
+          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -21234,12 +21238,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001535865</t>
+          <t>C001540447</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C001535865 - NANAJUARI CALDERON HILDA YOVANA</t>
+          <t>C001540447 - INVERSIONES ROCELI S.A.C.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -21286,13 +21290,17 @@
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21324,12 +21332,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C001481930</t>
+          <t>C001535865</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
+          <t>C001535865 - NANAJUARI CALDERON HILDA YOVANA</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -21376,17 +21384,13 @@
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21418,12 +21422,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C001612448</t>
+          <t>C001492706</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
+          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -21512,12 +21516,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001572913</t>
+          <t>C001481930</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C001572913 - CCAYCO CANALES MARISA</t>
+          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -21606,12 +21610,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001577373</t>
+          <t>C001360879</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C001577373 - CONTRERAS GUERRERO LISBET</t>
+          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21637,11 +21641,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
@@ -21667,12 +21667,12 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21704,12 +21704,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001492706</t>
+          <t>C001197394</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
+          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -22354,12 +22354,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C004206356</t>
+          <t>C004209286</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C004206356 - MINAS CHACALIAZA SILVIA MARIELA</t>
+          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -22448,12 +22448,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004209286</t>
+          <t>C004206356</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
+          <t>C004206356 - MINAS CHACALIAZA SILVIA MARIELA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -22542,12 +22542,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001016278</t>
+          <t>C001161300</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C001016278 - UNZUETA DE CHAVEZ HILDA ROSALIA</t>
+          <t>C001161300 - RIVERA GOMEZ ANGEL RENE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22594,13 +22594,17 @@
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22632,12 +22636,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001161300</t>
+          <t>C001016278</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001161300 - RIVERA GOMEZ ANGEL RENE</t>
+          <t>C001016278 - UNZUETA DE CHAVEZ HILDA ROSALIA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -22684,17 +22688,13 @@
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22910,12 +22910,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C001576771</t>
+          <t>C001565010</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001576771 - FLORES DE RAMOS LOURDES YOVANA</t>
+          <t>C001565010 - PISCONTE FRANCO YENI MARIELA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -22967,12 +22967,12 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23188,12 +23188,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001565010</t>
+          <t>C001674222</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C001565010 - PISCONTE FRANCO YENI MARIELA</t>
+          <t>C001674222 - SALCEDO ESPARZA DAVID LUIS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -23282,12 +23282,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001674222</t>
+          <t>C001576771</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C001674222 - SALCEDO ESPARZA DAVID LUIS</t>
+          <t>C001576771 - FLORES DE RAMOS LOURDES YOVANA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -23339,12 +23339,12 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23376,12 +23376,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C004048221</t>
+          <t>C001761926</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C004048221 - ELISORA S.A.C.</t>
+          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -23433,12 +23433,12 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23470,12 +23470,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C004023355</t>
+          <t>C004048221</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C004023355 - DELGADO CALLE ENA LUZ</t>
+          <t>C004048221 - ELISORA S.A.C.</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23511,7 +23511,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -23527,12 +23527,12 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23564,12 +23564,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>C001761926</t>
+          <t>C004023355</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
+          <t>C004023355 - DELGADO CALLE ENA LUZ</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -24304,12 +24304,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C001710219</t>
+          <t>C001683409</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>C001710219 - ESCALANTE LAGOS GERARDO JESUS</t>
+          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24361,12 +24361,12 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24398,12 +24398,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C001683409</t>
+          <t>C001710219</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
+          <t>C001710219 - ESCALANTE LAGOS GERARDO JESUS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24455,12 +24455,12 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C000872408</t>
+          <t>C000881799</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C000872408 - CORDOVA AGUILAR FAUSTA</t>
+          <t>C000881799 - BLONDET ALTAMIRANO MARLENI ESMERALDA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -25014,13 +25014,17 @@
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25052,12 +25056,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C000881799</t>
+          <t>C001161299</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C000881799 - BLONDET ALTAMIRANO MARLENI ESMERALDA</t>
+          <t>C001161299 - PARADO PEREZ SANTA BENITA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -25109,12 +25113,12 @@
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25240,12 +25244,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C001161299</t>
+          <t>C001198026</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C001161299 - PARADO PEREZ SANTA BENITA</t>
+          <t>C001198026 -  VARGAS ANCCANA KELLY JUDITH</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -25334,12 +25338,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>C001198026</t>
+          <t>C000872408</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>C001198026 -  VARGAS ANCCANA KELLY JUDITH</t>
+          <t>C000872408 - CORDOVA AGUILAR FAUSTA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -25386,17 +25390,13 @@
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr"/>
       <c r="V268" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25428,12 +25428,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C001489958</t>
+          <t>C001397200</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C001489958 - HINOSTROZA VILCAPUMA LUZMILA ALEXANDRA</t>
+          <t>C001397200 - PUJAIS VASQUEZ ROSANA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -25518,12 +25518,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001397200</t>
+          <t>C001445071</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>C001397200 - PUJAIS VASQUEZ ROSANA</t>
+          <t>C001445071 - MEJIA GALINDO FACUNDINA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -25570,13 +25570,17 @@
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25608,12 +25612,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001445071</t>
+          <t>C001489958</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>C001445071 - MEJIA GALINDO FACUNDINA</t>
+          <t>C001489958 - HINOSTROZA VILCAPUMA LUZMILA ALEXANDRA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -25660,17 +25664,13 @@
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr"/>
       <c r="V271" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25702,12 +25702,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C001492696</t>
+          <t>C001539717</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
+          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25796,12 +25796,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001551423</t>
+          <t>C001563527</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001551423 - MATA CUPE DYLAN RENATO</t>
+          <t>C001563527 - MINAYA RIOS DE MOGOLLON JESSICA VANESA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25848,13 +25848,17 @@
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25886,12 +25890,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001539717</t>
+          <t>C001551423</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
+          <t>C001551423 - MATA CUPE DYLAN RENATO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -25938,17 +25942,13 @@
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr"/>
       <c r="V274" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001563527</t>
+          <t>C001492696</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C001563527 - MINAYA RIOS DE MOGOLLON JESSICA VANESA</t>
+          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -26352,12 +26352,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C001539721</t>
+          <t>C004178774</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C001539721 - ALLCCAHUAMAN CAHUANA KAREN LISSET</t>
+          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -26404,13 +26404,17 @@
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26442,12 +26446,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C001634133</t>
+          <t>C004171458</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C001634133 - CHINCHAY GARCIA ANA MARIA</t>
+          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -26488,7 +26492,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S280" t="inlineStr"/>
@@ -26499,12 +26503,12 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26536,12 +26540,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C001752398</t>
+          <t>C004059422</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C001752398 - HUALPA GUEVARA ANDERSON PAUL</t>
+          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -26593,12 +26597,12 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26630,12 +26634,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C001749448</t>
+          <t>C004009751</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
+          <t>C004009751 - CULE QUISPE JOSE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -26687,12 +26691,12 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26724,12 +26728,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001708339</t>
+          <t>C004044936</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001708339 - ESCALANTE SALCEDO MILTON EUSTAQUIO</t>
+          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -26781,12 +26785,12 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26818,12 +26822,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C001709581</t>
+          <t>C001539721</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C001709581 - QUINONEZ ANTAYA EVA MARGARITA</t>
+          <t>C001539721 - ALLCCAHUAMAN CAHUANA KAREN LISSET</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -26870,17 +26874,13 @@
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26912,12 +26912,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C004178774</t>
+          <t>C001634133</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
+          <t>C001634133 - CHINCHAY GARCIA ANA MARIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -26969,12 +26969,12 @@
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27006,12 +27006,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C004171458</t>
+          <t>C001708339</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
+          <t>C001708339 - ESCALANTE SALCEDO MILTON EUSTAQUIO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S286" t="inlineStr"/>
@@ -27063,12 +27063,12 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27100,12 +27100,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C004044936</t>
+          <t>C001709581</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
+          <t>C001709581 - QUINONEZ ANTAYA EVA MARGARITA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -27157,12 +27157,12 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27194,12 +27194,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C004009751</t>
+          <t>C001752398</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C004009751 - CULE QUISPE JOSE</t>
+          <t>C001752398 - HUALPA GUEVARA ANDERSON PAUL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -27288,12 +27288,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C004059422</t>
+          <t>C001749448</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
+          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -27382,12 +27382,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C000881347</t>
+          <t>C001368530</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C000881347 - ALEJO CORNEJO ANA MARITZA</t>
+          <t>C001368530 - DE LA CRUZ VARGAS SAMUEL</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -27476,12 +27476,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C000881499</t>
+          <t>C000881347</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C000881499 - PALLIN QUISPE HAYDEE MARTINA</t>
+          <t>C000881347 - ALEJO CORNEJO ANA MARITZA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -27533,12 +27533,12 @@
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27570,12 +27570,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001368530</t>
+          <t>C000881499</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C001368530 - DE LA CRUZ VARGAS SAMUEL</t>
+          <t>C000881499 - PALLIN QUISPE HAYDEE MARTINA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -27627,12 +27627,12 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27942,12 +27942,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C001686242</t>
+          <t>C001362233</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C001686242 - SALVADOR ESPINOZA LUZ HERMINIA</t>
+          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -28032,12 +28032,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C001748378</t>
+          <t>C001552894</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
+          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -28084,17 +28084,13 @@
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28126,12 +28122,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001748916</t>
+          <t>C001686242</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
+          <t>C001686242 - SALVADOR ESPINOZA LUZ HERMINIA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -28178,17 +28174,13 @@
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28220,12 +28212,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001362233</t>
+          <t>C001748378</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
+          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -28272,13 +28264,17 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28310,12 +28306,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>C001552894</t>
+          <t>C001748916</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
+          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -28362,13 +28358,17 @@
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28400,12 +28400,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>C001069416</t>
+          <t>C000875203</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>C001069416 - CUCHO MITACC GABILU MILAGROS</t>
+          <t>C000875203 - ROSAS NIETO JUAN</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -28494,12 +28494,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C000877090</t>
+          <t>C001069416</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
+          <t>C001069416 - CUCHO MITACC GABILU MILAGROS</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -28551,12 +28551,12 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28776,12 +28776,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C000875203</t>
+          <t>C000877090</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>C000875203 - ROSAS NIETO JUAN</t>
+          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -28833,12 +28833,12 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28870,12 +28870,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C001443020</t>
+          <t>C001506611</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
+          <t>C001506611 - RONCEROS RIVERA DE GONZALES AGUEDA DEL R</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -29058,12 +29058,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>C001506611</t>
+          <t>C001638974</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>C001506611 - RONCEROS RIVERA DE GONZALES AGUEDA DEL R</t>
+          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C000875215</t>
+          <t>C001443020</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
+          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -29209,12 +29209,12 @@
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29246,12 +29246,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C000875926</t>
+          <t>C000875215</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>C000875926 - QUISPE CACERES DORIS</t>
+          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -29340,12 +29340,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C000877829</t>
+          <t>C000875926</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C000877829 - MATIAS CHAUPIN OLGA</t>
+          <t>C000875926 - QUISPE CACERES DORIS</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -29397,12 +29397,12 @@
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29434,12 +29434,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C001638974</t>
+          <t>C000877829</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
+          <t>C000877829 - MATIAS CHAUPIN OLGA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -29716,12 +29716,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C004243810</t>
+          <t>C004207402</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
+          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -29773,12 +29773,12 @@
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29810,12 +29810,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C004239540</t>
+          <t>C004191301</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
+          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -29867,12 +29867,12 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29904,12 +29904,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C004207402</t>
+          <t>C004191304</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
+          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -29961,12 +29961,12 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29998,12 +29998,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>C004191301</t>
+          <t>C004239540</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
+          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30092,12 +30092,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>C004191304</t>
+          <t>C004243810</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
+          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C004179837</t>
+          <t>C000881830</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>C004179837 - CONCA FLORES DORA ESTHER</t>
+          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -30243,12 +30243,12 @@
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30280,12 +30280,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C001683408</t>
+          <t>C000874788</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
+          <t>C000874788 - HUAMANI AVALOS NURY JULY</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -30337,12 +30337,12 @@
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30374,12 +30374,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C001708610</t>
+          <t>C000874272</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>C001708610 - SALAZAR YALLE FIORELLA ESTEFANI</t>
+          <t>C000874272 - LEGUA MEJIA FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -30405,7 +30405,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
@@ -30426,13 +30430,17 @@
       <c r="S322" t="inlineStr"/>
       <c r="T322" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30464,12 +30472,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>C001709978</t>
+          <t>C004179837</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
+          <t>C004179837 - CONCA FLORES DORA ESTHER</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -30521,12 +30529,12 @@
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30558,12 +30566,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>C004192500</t>
+          <t>C001683408</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>C004192500 - CORTEZ FLORES PATRICIA ELIZABETH</t>
+          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -30615,12 +30623,12 @@
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30652,12 +30660,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>C001284711</t>
+          <t>C001708610</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
+          <t>C001708610 - SALAZAR YALLE FIORELLA ESTEFANI</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -30704,17 +30712,13 @@
       <c r="S325" t="inlineStr"/>
       <c r="T325" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr"/>
       <c r="V325" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -30746,12 +30750,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C000881830</t>
+          <t>C001709978</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
+          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -30840,12 +30844,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C000874788</t>
+          <t>C004192500</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C000874788 - HUAMANI AVALOS NURY JULY</t>
+          <t>C004192500 - CORTEZ FLORES PATRICIA ELIZABETH</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -30934,12 +30938,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>C000874272</t>
+          <t>C001471930</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>C000874272 - LEGUA MEJIA FLOR DE MARIA</t>
+          <t>C001471930 - VICUNA REYES RAMON LINO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -30965,11 +30969,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
@@ -30995,12 +30995,12 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31032,12 +31032,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>C001471930</t>
+          <t>C001722065</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>C001471930 - VICUNA REYES RAMON LINO</t>
+          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -31063,7 +31063,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr"/>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -31089,12 +31093,12 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -31126,12 +31130,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>C001547860</t>
+          <t>C001506102</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
+          <t>C001506102 - QUICHUA ARROYO MARILU</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -31220,12 +31224,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>C001615633</t>
+          <t>C001284711</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
+          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -31266,7 +31270,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S331" t="inlineStr"/>
@@ -31314,12 +31318,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>C001506102</t>
+          <t>C001547860</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>C001506102 - QUICHUA ARROYO MARILU</t>
+          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -31408,12 +31412,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>C001722065</t>
+          <t>C001615633</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
+          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -31439,11 +31443,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M333" t="inlineStr"/>
       <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
@@ -31458,7 +31458,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S333" t="inlineStr"/>
@@ -31506,12 +31506,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>C004189020</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>C004189020 - HUAMAN VARGAS ENMA</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -31600,12 +31600,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>C001712478</t>
+          <t>C000874379</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>C001712478 - BENDEZU FERREYRA NER AMILCAR</t>
+          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -31657,12 +31657,12 @@
       </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31694,12 +31694,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>C001712482</t>
+          <t>C000872350</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>C001712482 - CANALES ROJAS OLGA</t>
+          <t>C000872350 - ORTIZ LINARES DE LILY</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -31746,13 +31746,17 @@
       <c r="S336" t="inlineStr"/>
       <c r="T336" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31784,12 +31788,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>C001716777</t>
+          <t>C000882632</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>C001716777 - DE LA CRUZ TORREALVA VICTOR PERCY</t>
+          <t>C000882632 - RAMIREZ VICU A JULIA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -31841,12 +31845,12 @@
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -32066,12 +32070,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>C004205639</t>
+          <t>C001390551</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
+          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -32160,12 +32164,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>C004048358</t>
+          <t>C001392849</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>C004048358 - GONZALES RODRIGUEZ LUZMILA</t>
+          <t>C001392849 - SOTOMAYOR BUSTAMANTE MERCEDES DEL CARMEN</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -32212,13 +32216,17 @@
       <c r="S341" t="inlineStr"/>
       <c r="T341" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U341" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -32250,12 +32258,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>C001712479</t>
+          <t>C001448001</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>C001712479 - CHAUCA SAAVEDRA SONIA URCINA</t>
+          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -32344,12 +32352,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>C001518391</t>
+          <t>C001532191</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>C001518391 - DITOLVI VELASCO IBIS LORENA</t>
+          <t>C001532191 - MEDINA DE LA CRUZ ALEJANDRINA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -32380,7 +32388,7 @@
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
@@ -32438,12 +32446,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>C001532191</t>
+          <t>C001518391</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>C001532191 - MEDINA DE LA CRUZ ALEJANDRINA</t>
+          <t>C001518391 - DITOLVI VELASCO IBIS LORENA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -32474,7 +32482,7 @@
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr">
@@ -32532,12 +32540,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>C001390551</t>
+          <t>C001712478</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
+          <t>C001712478 - BENDEZU FERREYRA NER AMILCAR</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -32626,12 +32634,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>C001392849</t>
+          <t>C001712482</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>C001392849 - SOTOMAYOR BUSTAMANTE MERCEDES DEL CARMEN</t>
+          <t>C001712482 - CANALES ROJAS OLGA</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -32678,17 +32686,13 @@
       <c r="S346" t="inlineStr"/>
       <c r="T346" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr"/>
       <c r="V346" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -32720,12 +32724,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>C001448001</t>
+          <t>C001716777</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
+          <t>C001716777 - DE LA CRUZ TORREALVA VICTOR PERCY</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -32814,12 +32818,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C004048358</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C004048358 - GONZALES RODRIGUEZ LUZMILA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -32866,17 +32870,13 @@
       <c r="S348" t="inlineStr"/>
       <c r="T348" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr"/>
       <c r="V348" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -32908,12 +32908,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>C000872350</t>
+          <t>C001712479</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>C000872350 - ORTIZ LINARES DE LILY</t>
+          <t>C001712479 - CHAUCA SAAVEDRA SONIA URCINA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -33002,12 +33002,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>C000882632</t>
+          <t>C004189020</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>C000882632 - RAMIREZ VICU A JULIA</t>
+          <t>C004189020 - HUAMAN VARGAS ENMA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -33096,12 +33096,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>C000882129</t>
+          <t>C004205639</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>C000882129 - EL GOLFO SAC</t>
+          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -33153,12 +33153,12 @@
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V351" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -33190,12 +33190,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>C000881032</t>
+          <t>C000882854</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
+          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>C000874379</t>
+          <t>C000882129</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
+          <t>C000882129 - EL GOLFO SAC</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -33374,12 +33374,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>C000882854</t>
+          <t>C000881032</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
+          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
